--- a/scripts/chapters/cr001.xlsx
+++ b/scripts/chapters/cr001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\scripts\chapters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\p2n\scripts\chapters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A87AA02-15DF-49B5-B13A-4C625B4B0E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA74EEB-5480-4450-81DC-DF0C937FCAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18420" yWindow="1760" windowWidth="15620" windowHeight="18190" activeTab="7" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="29475" yWindow="525" windowWidth="14250" windowHeight="15255" firstSheet="5" activeTab="10" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,11 @@
     <sheet name="04" sheetId="10" r:id="rId6"/>
     <sheet name="05" sheetId="12" r:id="rId7"/>
     <sheet name="06" sheetId="13" r:id="rId8"/>
+    <sheet name="07" sheetId="14" r:id="rId9"/>
+    <sheet name="sd103" sheetId="15" r:id="rId10"/>
+    <sheet name="08" sheetId="16" r:id="rId11"/>
+    <sheet name="09" sheetId="17" r:id="rId12"/>
+    <sheet name="10" sheetId="18" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="636">
   <si>
     <t>speaker</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,10 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>명령에 복종하겠다'고는 하지만, 무슨 생각을 하는지 전혀 알 수 없는 사람과의 거리는, 어쩌면 생각보다 더 멀지도 모른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>알겠어 알겠어, 나 지금 얌전히 길 안내해 주고 있잖아? 그 괴물 좀 거두라고, 이 음침한 녀석 같으니.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -554,18 +555,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;vc&gt;나이팅게일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>images/01/09.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>images/03.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이런 %@#@#￥%... 수감자!!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -641,10 +634,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&lt;vc&gt;무전기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>교회에는 신도가 있고, 술집에는 취객이 있다.</t>
   </si>
   <si>
@@ -1621,6 +1610,629 @@
   <si>
     <t>이야, 국장님 말도 안 들어?! 지독한 놈! 보여주세요! 족쇄로! 호되게 교육해주시라고요!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'명령에 복종하겠다'고는 하지만, 무슨 생각을 하는지 전혀 알 수 없는 사람과의 거리는, 어쩌면 생각보다 더 멀지도 모른다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;vc&gt;나이팅게일&lt;/vc&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;vc&gt;무전기&lt;/vc&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/25.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30여 명의 패거리가 낡은 개조 창고를 포위해 공격하고 있다. 창고 꼭대기에 달린 부서지고 기울어진 십자가가, 이 전대미문의 치열한 전장을 내려다보고 있었다.</t>
+  </si>
+  <si>
+    <t>여기는 구원 병원이다. 병원은 전장 중앙에 있지만, 목표는 병원 지하에 있다.</t>
+  </si>
+  <si>
+    <t>어이구, 아직 구원 병원은 치지도 않았는데 벌써 내분이라니. 하여간 너희 갱단 버릇 어디 안 가는구나.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘라</t>
+  </si>
+  <si>
+    <t>○○, 내 뒤에 서, 저 녀석들한테 본때를 보여주지!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테드</t>
+  </si>
+  <si>
+    <t>이 갱단들 범상치 않아. 이미 변이의 영향을 많이 받았어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니, 곤잘레스 가의 고용군이다. 아마 그들도 소문을 듣고 물건을 빼앗으러 온 것 같군.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리가 늦었나 보네. 저 앞에 병원을 공격하는 갱단도 당신 부하들이야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어이~ 테드잖아? 오셨구만~ 그런데 어쩌나 한발 늦어서, 킥킥~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곤잘레스 조직원</t>
+  </si>
+  <si>
+    <t>죽여라, 죽여라, 죽여라!! 구원 병원은 우리 거야, 우리 거!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무리야, 무리, 무리! 저 녀석들 머리통이 내 파이프보다 딱딱한데, 이 **를 어떻게 이겨?! 헤카테, 와서 좀 도와줘!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나 버리고 가지 마!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤카테가 당신의 손을 붙잡고 어두운 뒷골목으로 들어갔다.</t>
+  </si>
+  <si>
+    <t>그녀는 골목 안쪽에 있는 쓰레기통을 보자 당신을 밀어 넣고는 뚜껑을 닫았고 순식간에 몰려오는 악취에 기절할 것만 같았다.</t>
+  </si>
+  <si>
+    <t>괴변체에 죽을 것인지? 지독한 냄새를 맡아서 죽을 것인지? 구분할 수가 없을 정도다. 본능적으로 뚜껑을 열자, 한 줄기의 빛이 들어와 당신 곁에 있는 새하얀 팔다리가 비쳤다.</t>
+  </si>
+  <si>
+    <t>우리가 적을 다 해치울 때까지 여기서 기다리세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너무 위험해요. 국장님, 이쪽으로 오세요!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/26.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기통 안, 바로 당신 곁에 아름다운 메이드 소녀가 누워 있었다.</t>
+  </si>
+  <si>
+    <t>새하얗고 가느다란 몸엔 상처가 가득했고 피부에는 얼룩이 져 있었다. 그녀는 눈을 동그랗게 뜬 채로 분노도, 온도도 느껴지지 않았다.</t>
+  </si>
+  <si>
+    <t>하지만 저들의 힘이 이렇게나 강하다니, 설마...?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바보 같은 놈들, 성급하긴...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다가가서 확인한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 당황을 자제하고 천천히 뒤로 물러나 소녀의 잔해에서 벗어나려 했다. 그러나 뒤로 물러난 손이 그대로 쓰레기 더미에 빠져 쓰레기통 속의 산사태를 일으켰다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 잔해는 그대로 당신 품에 안겼다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그것은 매우 단단하고 무거웠다. 부딪칠 때마다 금속 같은 소리가 났고, 당신을 접촉한 순간 소녀의 눈동자가 밝아졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 자신도 모르게 가까이 다가가 희미한 불빛 사이로 그 소녀를 바라보았다. 그녀의 몸은 아직 썩지 않았고 심지어 어떠한 악취도 나지 않았다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싸움에서 묻은 얼룩이 그녀의 얼굴에 튀어 감을 수 없는 눈동자가 더욱 슬프게 느껴졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손을 뻗어 얼룩을 닦아주려 했지만 접촉하는 순간 뭔가 움직이는 소리가 들렸고 소녀의 눈동자가 밝아졌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?! 수감자 반응?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파손된 메이드</t>
+  </si>
+  <si>
+    <t>파손된 메이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오, 오염 가, 감소. 오염 감소, 장애물 제거. 생물 중추, 되찾는 중.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그녀의 뺨에서 액체가 흘렀고, 관절이 갑자기 삐걱거리며 움직여 몸을 일으켰다. 그러더니 머리를 쓰레기통에 부딪혀 거대한 금속 충돌음을 냈다.</t>
+  </si>
+  <si>
+    <t>안녕하십니까, 당신을 위해 일할 III형 스마트 메이드 &lt;org&gt;레버린스&lt;/org&gt;입니다. 청소 프로세스를 시작하시겠습니까, 주인님?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초기화 완료, 재가동 성공.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나사 하나가 우수한 메이드 로봇의 몸에서 뿅 하고 튀어나왔다.</t>
+  </si>
+  <si>
+    <t>레버린스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간? 레버린스의 중추에는 인간의 완전한 신경계가 탑재되어 있습니다. 그렇다면 조금 인간 같나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수감자는 전부 인간이었는데.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>승리했습니다. 보호 대상이 무사합니다. 전투 지령 회수 성공. 안녕하세요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리를 기억해?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리? 데이터베이스 검색 시작. 검색 완료. 주인님의 기록뿐입니다. 당신께 중요한 사람입니까? 레버린스가 그녀를 찾아드리길 원하십니까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재가동. 시스템 재가동, 재가동 실패. 시스템 초기화, 기억 삭제... 작업, 전투... 커... 커피...</t>
+  </si>
+  <si>
+    <t>마... 마리...를 지켜야... 마... 리... 죄... 송... 합니다...</t>
+  </si>
+  <si>
+    <t>...로봇?</t>
+  </si>
+  <si>
+    <t>구원 병원...? 그래도 싸움이 끝나고, MBCC에 돌아가서 한번 봐줘야 할 것 같다. 기계로 된 몸은 고칠 수 있지만 레버린스의 기억은?</t>
+  </si>
+  <si>
+    <t>...필요없어. 난 걔가 누군지 모르는데, 뭐</t>
+  </si>
+  <si>
+    <t>...몰라.</t>
+  </si>
+  <si>
+    <t>우린 달라.</t>
+  </si>
+  <si>
+    <t>신기하네요. 당신, 저와 엄청 닮았습니다. 당신도 명령을 기다립니까?</t>
+  </si>
+  <si>
+    <t>동의합니다. 레버린스는 실제 상황에 맞게 스스로 명령을 생성할 수 있지만, 당신은 이러한 자체 성능을 가지고 있지 않습니다.</t>
+  </si>
+  <si>
+    <t>만족합니다. 도구로서는 레버린스가 더 우수합니다.</t>
+  </si>
+  <si>
+    <t>흐음, 이 신체는 손상 상태가 심각합니다. 수리점을 찾아야 합니다... 구원 병원, 의체 복구 센터입니다.</t>
+  </si>
+  <si>
+    <t>신청합니다. 주인님, 가장 아끼시는 메이드의 신체 수리를 위해 돈을 지불해주실 수 있으십니까?</t>
+  </si>
+  <si>
+    <t>주인님의 기분이 안 좋아 보입니다.</t>
+  </si>
+  <si>
+    <t>커피. 드시겠습니까? 레버린스가 가장 자신 있는 프로세스입니다. 분명 주인님을 기쁘게 할 수 있을 겁니다.</t>
+  </si>
+  <si>
+    <t>승리하기는 했으나, 테드의 부하는 아직도 패배한 상대를 때리고 있었다. 두 눈이 벌겋고, 날리는 펀치마다 죽을 힘을 다 해 때렸다.</t>
+  </si>
+  <si>
+    <t>바로 이때, 굳게 닫혀 있던 구원 병원의 문이 열리고 무장 의사들이 걸어 나왔다. 표정이 무척 심각했는데, 시린 증오로 가득 찬 것 같았다.</t>
+  </si>
+  <si>
+    <t>그가 갑자기 발버둥을 치며 내 발목을 잡았고, 차갑고 단단한 의수에 발걸음이 멈췄다.</t>
+  </si>
+  <si>
+    <t>images/01/27.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/28.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테드가 그를 걷어차 떼어내고, 당신을 옆으로 끌어당겼다.</t>
+  </si>
+  <si>
+    <t>급히 뒤를 돌자, 아까 왔던 방향 쪽에서 피어오르는 연기 사이로 그림자 하나가 일렁였다.</t>
+  </si>
+  <si>
+    <t>images/01/29.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사람을 구하러 간 것이었어?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구원 병원 구성원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국장님! 뒤에!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테드 부하들 보고 여길 떠나라고 해, 너무 위험해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아악!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테드 조직원</t>
+  </si>
+  <si>
+    <t>그만해! 이 ** 나한테 졌던 녀석이야, 누가 이렇게 죽도록 패래? 비! 키! 라! 고~!!</t>
+  </si>
+  <si>
+    <t>**, 힘이 왜 이렇게 세진 거야, 당겨지지가 않네.</t>
+  </si>
+  <si>
+    <t>무슨 헛소리야? 진짜로 부하가 걱정된다면 더 이상 무모한 짓을 하지 못하게 막아.</t>
+  </si>
+  <si>
+    <t>아니, 이건 천재일우의 기회다.</t>
+  </si>
+  <si>
+    <t>수감자에게 빌붙은 네가 무슨 자격으로 큰소리지?</t>
+  </si>
+  <si>
+    <t>가지, 국장. 들어가서 그 R을 찾아내자고.</t>
+  </si>
+  <si>
+    <t>정신 차려! 저들은 적군이야. 본인 위치를 잊지 마, 국장.</t>
+  </si>
+  <si>
+    <t>그들은 지금 통제를 잃고 변이되고 있어. 구원 병원에 가까워져서 영향을 받은 걸까.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이언 의사가 너희를 치료해 줄 것이다. 그녀가 돌아오기 전에 먼저 소독해두지.</t>
+  </si>
+  <si>
+    <t>그들에게 무슨 짓을 한 거야?!</t>
+  </si>
+  <si>
+    <t>하하, 뺏어보시지... 죽어... 죽어... 죽어!!</t>
+  </si>
+  <si>
+    <t>구원 병원은 지금 평범한 무장 의사들만 지키고 있어. 조금만 더 늦었다면 그 여자가 돌아왔을 거야. 그럼 여길 공격할 수 없었겠지...</t>
+  </si>
+  <si>
+    <t>비록 내 사람들이 변이체가 되어버렸지만... 힘을 얻기도 했지. 보이나? 그 녀석들이 맨손으로 곤잘레스를 때려죽였잖아!</t>
+  </si>
+  <si>
+    <t>이렇게나 오래 싸우고 저 많은 사람들을 꺾었는데, 여기서 멈출 순 없어. 이게 마지막 기회야. 내 부하들은 강해졌고, 여전히 전투를 할 수 있지, 조금만 더 하면...</t>
+  </si>
+  <si>
+    <t>멍청한 갱단 녀석들... 감히 구원 병원에서 폭력을 쓰려고 해? 뇌가 종기로 가득 찬 쓰레기들답군.</t>
+  </si>
+  <si>
+    <t>큭... 이 수감자들만 아니었어도...</t>
+  </si>
+  <si>
+    <t>테드, 부하들이 변이체에 접촉하도록 그냥 내버려 두다니... 당신... 그 결과는 알고 있는 건가?!</t>
+  </si>
+  <si>
+    <t>너희들이 멋대로 구는 것도 이제는 지긋지긋하다... 그 괴물들을 쫓아낼 수만 있다면, 신디케이트가 예전으로 돌아갈 수만 있다면, 난 무엇이든 할 수 있어.</t>
+  </si>
+  <si>
+    <t>당신... 부끄러운 줄도 모르고...</t>
+  </si>
+  <si>
+    <t>브랜드... 그리고 로라... 우리 외근팀이... 구조하러 나갔다가 다시 돌아오지 않았는데, 무슨 일이 있었나?</t>
+  </si>
+  <si>
+    <t>브랜드 의사는 사람을 구하러 갔어. 너희처럼 구원 병원을 포위 공격하고, 또 서로 잔인하게 죽여대는 자들을 말이야. 그 한 치의 시간 오차 없이 정교한 수술하는 사람이 제시간에 돌아오지 않았단 말이다...</t>
+  </si>
+  <si>
+    <t>...그 얼굴을, 그리고 피로 물든 흰옷도 알아볼 수 있었다.</t>
+  </si>
+  <si>
+    <t>images/01/30.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테드가 총을 들어 자신의 손에서 살아남은 남자를 겨눴다.</t>
+  </si>
+  <si>
+    <t>멈춰, 테드!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그의 총은 정말 빠르다. 총알이 날아갔지만, 브랜드에게 닿기 직전 검은 기류에 의해 튕겨져 나갔다.</t>
+  </si>
+  <si>
+    <t>무엇이 그를 움직이게 하는 걸까.</t>
+  </si>
+  <si>
+    <t>images/01/31.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순식간에 벌어진 일이었다. 검은 가시가 포효하듯 브랜드의 몸에서 방사되듯 솟아났고, 이내 금방 구부러지듯 모양을 바꿔 몸속으로 들어갔다.</t>
+  </si>
+  <si>
+    <t>그리고 그의 외형이 완전히 변했다. 제어할 수 없는 분노로 진짜 괴물이 된 것이다.</t>
+  </si>
+  <si>
+    <t>images/01/32.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>...금방 갈게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'브랜드'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바로 그 순간, 그에게서 뭔가 수감자와 비슷한 냄새가 났다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손가락 길이 정도 되는 금속 원기둥 하나가 근처로 굴러와 천천히 멈췄다. 치익 소리와 함께 양 끝 구멍에서 이상한 가스가 뿜어져 나왔다.</t>
+  </si>
+  <si>
+    <t>엘라가 새파랗게 질린 얼굴로 달려들었지만, 닿기도 전에 어떤 엄청난 힘에 의해 내쳐졌다.</t>
+  </si>
+  <si>
+    <t>엘라를 잡는다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손을 뻗으려 했지만, 손이 제 높이까지 올라가지 않았다. 그렇게 시야가 흔들리기 시작하더니, 아래로 곤두박질쳤다.</t>
+  </si>
+  <si>
+    <t>얼른 피한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 의심스러운 가스를 피하려고 했지만 다리가 제대로 몸을 따르지 않아 곧장 뒤로 넘어져 버렸다. 그럼에도 고통은 느껴지지 않았다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소리치고 싶었지만, 마치 의식과 육체의 연결이 끊어진 것처럼 입술과 혀가 말을 듣지 않았다. 희미하게 흔들리는 시야만이 마지막으로 붙잡을 수 있는 유일한 부목 같은 존재였다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/33.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브랜드 선생!! 아직 살아있었군!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쳇.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘라, 국장님을 지켜.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 아닙니다. 저건 괴변체예요, 더 강한 괴변체.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국장님, 병원으로 들어가시죠.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 됐습니다. 무장 의사도 처리했고, 아무도 우릴 방해할 수 없어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막으로 바닥에 쓰러진 '브랜드'에게 다가갔다. 그의 동공은 점점 풀려가고, 입에서는 무언가를 여전히 중얼거리고 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막으로 바닥에 쓰러진 '괴물'을, '브랜드'를 바라봤다. 그의 동공은 점점 풀려가고, 입에서는 무언가를 여전히 중얼거리고 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브랜드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하! 하하! 죽여버려, 죽여버린다!! 내가! 내가 할 거야!!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!! 그 녀석 잡아! 가까이 가게 두지 마!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으아아!!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>브랜드 선생!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저건 변이체예요. 그의 힘... 매우 강합니다. 다른 사람들이랑은 차원이 달라요.</t>
+  </si>
+  <si>
+    <t>그는 수감자인가? 아니, 아니다. 하지만 그는 갱단 변이체들과도 다르다. 주변의 검은 연기가 마치 그의 지휘를 따르는 것 같다. 게다가...</t>
+  </si>
+  <si>
+    <t>...그라... 함... 그리고...</t>
+  </si>
+  <si>
+    <t>...로라, 울지 마... 로라... 이제 아무도 널 해치지 못해...</t>
+  </si>
+  <si>
+    <t>이건 진짜가 아니야... 브랜드... 설마 너도...</t>
+  </si>
+  <si>
+    <t>너희 다 미쳤어!? 가지 마, 그는...</t>
+  </si>
+  <si>
+    <t>...아아... 으아아아!!!</t>
+  </si>
+  <si>
+    <t>저... 저게 뭐야? 저게 진짜... 방금 그 사람이라고?</t>
+  </si>
+  <si>
+    <t>너희를 다치게 하는 놈들은... 모두... 죽인다...!!!</t>
+  </si>
+  <si>
+    <t>후우... 후... 우리 같은 사람이 저런 괴물을 상대하게 될 줄은 몰랐는데...</t>
+  </si>
+  <si>
+    <t>정말 최악이군, 테드 그 자식... **, 너무 멀리 도망간 거 아냐?! 남하고 척 지는 게 그렇게 무섭대?!</t>
+  </si>
+  <si>
+    <t>내가... 너희들을... 구할 거야... 내가...</t>
+  </si>
+  <si>
+    <t>팅... 팅... 타다닥...</t>
+  </si>
+  <si>
+    <t>엘라: 이건!? 숨 쉬지 마, ○○! 안...</t>
+  </si>
+  <si>
+    <t>......신경... 독... 소...</t>
+  </si>
+  <si>
+    <t>...당직 끝났어... 브랜드... 푹 쉬어...</t>
+  </si>
+  <si>
+    <t>......그리고, 구원 병원에 온 걸 환영해... 졸개 국장.</t>
+  </si>
+  <si>
+    <t>images/01/34.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/35.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낡고 어수선한 공간. 공기 중에 먼지가 나부끼고, 피비린내가 섞인 썩은 소독약 냄새가 났다.</t>
+  </si>
+  <si>
+    <t>부산스러운 사람 소리와 울부짖는 소리가 층을 걸러 들려온다. 처절하지만 아득하다.</t>
+  </si>
+  <si>
+    <t>고통도 없고, 속박당하지도 않은 상태를 보니 아직 뭔가를 당하지는 않은 듯하다. 안도의 한숨이 절로 나왔다.</t>
+  </si>
+  <si>
+    <t>곁눈질로 주위를 둘러보니 사방에서 에워싸고 지켜보던 사람들은 이미 흩어진 채였다.</t>
+  </si>
+  <si>
+    <t>엘라와 헤카테는 없지만, 이 근처에 있음을 느낄 수 있었다.</t>
+  </si>
+  <si>
+    <t>찾으러 가자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회색빛 긴 머리에 창백한 얼굴, 총상을 감싼 피투성이 붕대.</t>
+  </si>
+  <si>
+    <t>아는 얼굴이다. 화라고는 조금도 찾아볼 수 없는 이 얼굴은 절대 잊지 못할 것이다. 생명을 위협받던 기억이 떠올라 몸에서 식은땀이 줄줄 흘렀다.</t>
+  </si>
+  <si>
+    <t>images/01/36.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>images/01/37.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삐... 삐... 삐... 삐...</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ...엘라? 헤카테...?</t>
+  </si>
+  <si>
+    <t>여긴... 어디지?</t>
+  </si>
+  <si>
+    <t>당신들 누구야...?</t>
+  </si>
+  <si>
+    <t>두 수감자...? 그 애들에게 무슨 짓을 한 거야?</t>
+  </si>
+  <si>
+    <t>몸을 일으키려고 고개를 돌렸고, 곧이어 시야에 들어온 것은...</t>
+  </si>
+  <si>
+    <t>...그 살인마였다. 그가 고개를 돌려 당신을 바라본다.</t>
+  </si>
+  <si>
+    <t>...반응 있고... EEG 활발함...</t>
+  </si>
+  <si>
+    <t>...좋아, 18번 자리는 0.7로 빈도를 낮춰서 정확하게 기록하고...</t>
+  </si>
+  <si>
+    <t>...구조 안정적... 기억 손상... 생리적 문제 없음...</t>
+  </si>
+  <si>
+    <t>잡음이 좀 있군... 좀 더 억제해... M 수치는 어때? 위험한가?</t>
+  </si>
+  <si>
+    <t>......파동이 없다고?... 측량 정도의 문제가 아닌 게 확실해?</t>
+  </si>
+  <si>
+    <t>...............그럴 리가... 그렇게 많은 변이체들과 접촉했는데...</t>
+  </si>
+  <si>
+    <t>...그 두 수감자는 어때...</t>
+  </si>
+  <si>
+    <t>...더 억제해...</t>
+  </si>
+  <si>
+    <t>...그런가... 그녀들도... 그렇게 소란을 피웠으면서도 안정적이군...</t>
+  </si>
+  <si>
+    <t>......관리국의 기술인가... 아님 그냥 이 사람이...</t>
+  </si>
+  <si>
+    <t>흠흠... 제대로 연구해봐야겠네... 그녀가 관건일 것 같은 예감이 들어...</t>
+  </si>
+  <si>
+    <t>...그녀와 함께... 어떤... 변화가... 있는지... 보자고...</t>
   </si>
 </sst>
 </file>
@@ -1707,8 +2319,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1728,9 +2340,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1768,7 +2380,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1874,7 +2486,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2016,7 +2628,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2025,15 +2637,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEC9E4D-1BC2-47C1-B354-5864E5DC6C7E}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="4" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2059,12 +2671,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="48" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2072,7 +2684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="54" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -2080,7 +2692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2088,15 +2700,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2104,7 +2716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2115,7 +2727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -2123,7 +2735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2134,17 +2746,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2152,17 +2764,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
@@ -2170,12 +2782,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
@@ -2183,7 +2795,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -2191,12 +2803,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="64" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="54" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>9</v>
       </c>
@@ -2204,7 +2816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
@@ -2212,7 +2824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
@@ -2220,12 +2832,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
@@ -2233,7 +2845,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>10</v>
       </c>
@@ -2241,12 +2853,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C27" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -2254,17 +2866,1376 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54D5E28-54CD-49E3-9E8A-99957D4982A5}">
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C8" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C13" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C26" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C42" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B44" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>517</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9AFAB1-D13F-453B-A764-71BC4DD03FA9}">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C15" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="6" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C37" s="6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930164D6-DE97-4948-9170-1B29F324C0A0}">
+  <dimension ref="A1:H53"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="6" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C8" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C20" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C21" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C42" s="6" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C44" s="6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C50" s="6" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307336A0-8DF1-492D-89DC-9934A1DE74C4}">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C21" s="6" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C22" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C23" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C24" s="6" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="6" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="6" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C30" s="6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C32" s="6" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -2277,15 +4248,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7115359D-7475-477E-8932-F919DE4EA60B}">
   <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2311,12 +4282,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
@@ -2324,7 +4295,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -2332,7 +4303,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -2340,7 +4311,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2351,7 +4322,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2359,7 +4330,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2370,12 +4341,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
@@ -2383,7 +4354,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2391,12 +4362,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C12" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
@@ -2404,7 +4375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
@@ -2412,12 +4383,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C15" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2425,7 +4396,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
@@ -2433,7 +4404,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
@@ -2441,7 +4412,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -2449,7 +4420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -2457,386 +4428,386 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C21" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C22" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C25" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C28" s="6" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C29" s="6" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C31" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C31" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C37" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C37" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C40" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C40" s="6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C44" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C44" s="6" t="s">
+    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C45" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C45" s="6" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B46" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" s="6" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C47" s="6" t="s">
+    <row r="49" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C49" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B48" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C49" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B53" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C53" s="6" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C55" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C56" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C55" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C56" s="6" t="s">
+      <c r="C57" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B60" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B57" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B58" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B59" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B60" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C61" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B62" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C63" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B64" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C63" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B64" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B67" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C67" s="6" t="s">
+    <row r="68" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B68" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B70" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B71" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B70" s="3" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B73" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B71" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C72" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B73" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B75" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B75" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C75" s="6" t="s">
+    <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B76" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B76" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2848,16 +4819,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EB44A9-9BB2-4DDC-B33A-B25D27D1D6DE}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.58203125" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2883,218 +4854,213 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>133</v>
+        <v>455</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>133</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>455</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="6" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C15" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="6" t="s">
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C17" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B23" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>10</v>
+        <v>455</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B26" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="6" t="s">
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B27" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="6" t="s">
+    <row r="29" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B29" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B31" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -3107,15 +5073,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB64E87-5691-4BF1-B88C-0D9BCA723708}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.58203125" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3141,438 +5107,438 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>155</v>
+        <v>456</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C19" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C20" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C22" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C23" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C25" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C20" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C22" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C23" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C25" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C30" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="C35" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F36" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F37" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F38" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="27" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C46" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C47" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C55" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C56" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B58" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C59" s="6" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C62" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3585,15 +5551,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85819A9-A6A1-4AA6-96F8-1AFF8AF47654}">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3619,345 +5585,345 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C6" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C7" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C14" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C25" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C27" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B34" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C35" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -3970,15 +5936,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967F6D5D-D295-422A-9553-A28D16FBCF3E}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4004,161 +5970,161 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C4" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="C12" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C15" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="32" x14ac:dyDescent="0.45">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="32" x14ac:dyDescent="0.45">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="32" x14ac:dyDescent="0.45">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -4171,15 +6137,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A7FE47-AF86-403F-8DF9-F647B1E34428}">
   <dimension ref="A1:H82"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4205,592 +6171,592 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C5" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.45">
-      <c r="C5" s="6" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="C12" s="6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C26" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C30" s="6" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C10" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C11" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B18" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B19" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B22" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B23" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B25" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C26" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B27" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B28" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C29" s="6" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C30" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C37" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C38" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C42" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B45" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B45" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B46" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B47" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B48" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B52" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B53" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C54" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C55" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C56" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C61" s="6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C62" s="6" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B64" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C69" s="6" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C73" s="6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C76" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B77" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B79" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B80" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" ht="48" x14ac:dyDescent="0.45">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C81" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" ht="48" x14ac:dyDescent="0.45">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C82" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -4803,15 +6769,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A100192-05EB-4836-9F6B-C6DB0E932DAB}">
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.6640625" style="2"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4837,570 +6803,570 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C7" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C14" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B5" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C7" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B9" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C10" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C11" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
-      <c r="C14" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C23" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C27" s="6" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="B22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C23" s="6" t="s">
+    <row r="28" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C24" s="6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B26" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C27" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C28" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C31" s="6" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C33" s="6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C36" s="6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C41" s="6" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B45" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
       <c r="C46" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="C49" s="6" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A47" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B48" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C49" s="6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C51" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C53" s="6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B61" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C63" s="6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C64" s="6" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C65" s="6" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B67" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B70" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C73" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C75" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B76" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C77" s="6" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -5408,10 +7374,10 @@
         <v>10</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -5419,10 +7385,10 @@
         <v>10</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -5430,40 +7396,40 @@
         <v>10</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -5471,63 +7437,194 @@
         <v>10</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A88" s="8" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="A89" s="8" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C90" s="6" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="B91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B92" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B93" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C94" s="6" t="s">
-        <v>416</v>
+        <v>412</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA34A18B-B515-443B-8160-8DC81D3CB263}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="4" max="8" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="C4" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/chapters/cr001.xlsx
+++ b/scripts/chapters/cr001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\temp\p2n\scripts\chapters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\scripts\chapters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA74EEB-5480-4450-81DC-DF0C937FCAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA5FE2B-C091-4177-8A1E-F6FB9781BFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29475" yWindow="525" windowWidth="14250" windowHeight="15255" firstSheet="5" activeTab="10" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="18420" yWindow="1760" windowWidth="15620" windowHeight="18190" firstSheet="5" activeTab="13" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="08" sheetId="16" r:id="rId11"/>
     <sheet name="09" sheetId="17" r:id="rId12"/>
     <sheet name="10" sheetId="18" r:id="rId13"/>
+    <sheet name="mz01" sheetId="20" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="684">
   <si>
     <t>speaker</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1746,10 +1747,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>?! 수감자 반응?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>파손된 메이드</t>
   </si>
   <si>
@@ -1779,10 +1776,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>인간? 레버린스의 중추에는 인간의 완전한 신경계가 탑재되어 있습니다. 그렇다면 조금 인간 같나요?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수감자는 전부 인간이었는데.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1802,9 +1795,6 @@
     <t>재가동. 시스템 재가동, 재가동 실패. 시스템 초기화, 기억 삭제... 작업, 전투... 커... 커피...</t>
   </si>
   <si>
-    <t>마... 마리...를 지켜야... 마... 리... 죄... 송... 합니다...</t>
-  </si>
-  <si>
     <t>...로봇?</t>
   </si>
   <si>
@@ -2074,10 +2064,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>!! 그 녀석 잡아! 가까이 가게 두지 마!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>으아아!!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2104,9 +2090,6 @@
     <t>너희 다 미쳤어!? 가지 마, 그는...</t>
   </si>
   <si>
-    <t>...아아... 으아아아!!!</t>
-  </si>
-  <si>
     <t>저... 저게 뭐야? 저게 진짜... 방금 그 사람이라고?</t>
   </si>
   <si>
@@ -2232,7 +2215,190 @@
     <t>흠흠... 제대로 연구해봐야겠네... 그녀가 관건일 것 같은 예감이 들어...</t>
   </si>
   <si>
-    <t>...그녀와 함께... 어떤... 변화가... 있는지... 보자고...</t>
+    <t>?!&lt;br&gt;수감자 반응?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마... 마리...를 지켜야... 마... 리...&lt;br&gt;죄... 송... 합니다...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;org&gt;인간&lt;/org&gt;? 레버린스의 중추에는 인간의 완전한 신경계가 탑재되어 있습니다. 그렇다면 조금 인간 같나요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>...아아...&lt;br&gt;으아아아!!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!!&lt;br&gt;그 녀석 잡아! 가까이 가게 두지 마!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>...&lt;org&gt;그녀&lt;/org&gt;와 함께... 어떤... 변화가... 있는지... 보자고...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추락 또 추락, 끝이 보이지 않는 추락. 눈을 떠보니 어둠만이 보이고, 사방에서 한기가 전해진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기다린다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>섣불리 행동하지 못한 채 가만히 있는데, 방 안은 코를 찌르는 소독약 냄새로 가득하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸깍.</t>
+  </si>
+  <si>
+    <t>기계 소리와 함께, 푸른빛이 희미하게 사방에 퍼진 안개를 밝힌다. 당신은 지금 병원의 긴 복도에 있다.</t>
+  </si>
+  <si>
+    <t>불을 켜도 냉기는 가시지 않고, 오히려 점점 서늘해져갈 뿐이었다. 시간이 지날수록 당신의 몸이 굳어간다.</t>
+  </si>
+  <si>
+    <t>이곳이 어디든 빨리 탈출하지 않으면 결말은 죽음뿐이다.</t>
+  </si>
+  <si>
+    <t>일어난다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일어서려 했지만 스위치가 켜진 듯 순식간에 냉기 가득한 안개가 피어오르고 진한 소독약 냄새가 몸을 감쌌다.</t>
+  </si>
+  <si>
+    <t>복도에서 문고리가 녹슬 대로 녹슬어있는 병실을 발견했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 문에 있는 유리 너머로 병상에 누워있는 인간형의 생명체가 보였다.</t>
+  </si>
+  <si>
+    <t>고름 덩어리로 뒤덮인 그의 몸은 피로 얼룩져있었다. 짙은 소독약 냄새에도 메스꺼운 썩은 냄새가 당신의 코를 찔렀다.</t>
+  </si>
+  <si>
+    <t>아파...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>살려줘... 살려줘...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 괴물은 병상에서 고통스럽게 으르릉거리며 몸부림치고 있었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>떠난다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화를 시도한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의식을 완전히 잃은 듯 반복해서 고함을 지를 뿐, 당신의 소리에도 아무런 반응이 없었다.</t>
+  </si>
+  <si>
+    <t>또 다른 병실, 어둠 속에서 아까와는 다른 것 같지만 익숙한 목소리가 들린다.</t>
+  </si>
+  <si>
+    <t>이빨 사이를 비집고 나오는 그의 말 마디 마디에는 감출 수 없는 원한이 서려 있었다.</t>
+  </si>
+  <si>
+    <t>병실 안에서 쿵쿵 두드리는 소리가 들렸고, 방문이 꽉 닫혀있음에도 본능적으로 공포가 느껴졌다.</t>
+  </si>
+  <si>
+    <t>이 생물들이 의식이 있든 없든 간에, 그곳에서 나오기만 한다면 망설임 없이 당신을 죽일 것이라는 확신이 들었다.</t>
+  </si>
+  <si>
+    <t>반드시 출구를 찾아 이곳, 이름 모를 병원을 떠나야 한다.</t>
+  </si>
+  <si>
+    <t>저주할 거야. 당신들은 죽음보다 더 못한 삶을 살 거야, 영원히!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽 병실 문이 활짝 열려 있다. 괴물 하나가 병실을 탈출해 복도를 기계적으로 돌아다니고 있었다.</t>
+  </si>
+  <si>
+    <t>그의 몸은 완전히 붕괴되었고, 일찍이 바닥에 떨어진 혈흔이 굳어 복도에 긴 흔적을 남겼다.</t>
+  </si>
+  <si>
+    <t>허무한 외침이 고요한 복도에 울려 퍼졌지만 끝내 아무 대답도 들리지 않았다.</t>
+  </si>
+  <si>
+    <t>복도에서 갈림길이 나왔다. 왼쪽에는 녹색 비상구 표시가, 오른쪽에는 '특수 병실 구역-01a'라는 빨간 문패가 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우릴 다 잊어버린 거야?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 병실의 모든 시설은 이미 산산조각이 나있었다. 탈출한 그 괴물이 부순 것이 분명했다.</t>
+  </si>
+  <si>
+    <t>희미한 불빛에 의지에 당신은 폐허 속에서 잘 보존된 투명한 약통을 하나 찾았다.</t>
+  </si>
+  <si>
+    <t>당신은 출구와 그 괴물을 번갈아보며 자신이 탈출할 수 있는지 의심한다. 하지만 그는 결국 이곳을 벗어나지 못한 것이 확실했다.</t>
+  </si>
+  <si>
+    <t>images/01/39.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[투명한 약상자]: 일주일 치 약상자. 3X7, 총 21개 칸으로 나뉘어있다. 월요일부터 일요일까지 글씨가 프린팅되어 있으며, 오른쪽 하단에는 흰색 라벨지가 붙어있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'이번 주 약을 다 먹으면 우리 모두 나갈 수 있어요.'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비상 탈출 표시를 따라 당신은 드디어 복도 끝에 도착했다. 열린 문 뒤로 따스하고 하얀 빛이 반짝인다.</t>
+  </si>
+  <si>
+    <t>당신이 오는 것을 아는 듯, 하얀 빛이 들어와 주변의 어둠을 걷어내고, 순간 안도감이 느껴진다. 이건 단지 악몽일 뿐, 이제 당신이 깨어날 차례이다.</t>
+  </si>
+  <si>
+    <t>하지만 희미한 빛 속에서 당신은 피투성이가 된 간호복을 입고 문 앞에서 무릎을 꿇고 있는 여인을 보았다.</t>
+  </si>
+  <si>
+    <t>그녀는 손으로 무언가를 적고 있었고, 그녀 뒤로 보이는 황량한 땅바닥에는 이름들이 빽빽하게 적혀 있었다.</t>
+  </si>
+  <si>
+    <t>여인의 옆에는 흰 천이 덮인 인형이 놓여 있는데, 그녀는 아직 당신의 존재를 모르는 듯 혼잣말을 속삭였다. 그러고는 어머니가 아이를 안듯 부드럽게 그 인형을 품에 안았다.</t>
+  </si>
+  <si>
+    <t>갑자기 당신의 발밑이 무너져 내리고, 몸이 아래로 곤두박질친다. 몸이 마음대로 움직이지 않는다. 놀란 마음에 옆에 있던 벽에 기대보려 했지만 벽 또한 빠르게 무너져 내린다.</t>
+  </si>
+  <si>
+    <t>허무함이 다시 당신을 집어삼키기 전에 그녀가 당신을 바라보았다.</t>
+  </si>
+  <si>
+    <t>여인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>............</t>
+  </si>
+  <si>
+    <t>의사... 의사, 다 어디로 간 거야?</t>
+  </si>
+  <si>
+    <t>내가 구해줄게...</t>
+  </si>
+  <si>
+    <t>약속했어. 내가 약속했어...</t>
+  </si>
+  <si>
+    <t>이건 3*7, 총 21개의 작은 칸으로 구성된 '주간 약통'이었다. 월요일부터 일요일까지의 요일 표기 문자 외에 견고하게 붙어 있는 라벨 용지도 눈에 띄었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2340,9 +2506,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2380,7 +2546,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2486,7 +2652,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2628,7 +2794,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2637,15 +2803,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FEC9E4D-1BC2-47C1-B354-5864E5DC6C7E}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="4" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2671,12 +2837,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -2684,7 +2850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -2692,7 +2858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2700,7 +2866,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -2708,7 +2874,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -2716,7 +2882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2727,7 +2893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -2735,7 +2901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2746,17 +2912,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2764,17 +2930,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="C15" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
@@ -2782,12 +2948,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
@@ -2795,7 +2961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -2803,12 +2969,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>9</v>
       </c>
@@ -2816,7 +2982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
@@ -2824,7 +2990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
@@ -2832,12 +2998,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>31</v>
       </c>
@@ -2845,7 +3011,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>10</v>
       </c>
@@ -2853,12 +3019,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C27" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
@@ -2866,12 +3032,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
@@ -2889,15 +3055,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C54D5E28-54CD-49E3-9E8A-99957D4982A5}">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2923,12 +3089,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
@@ -2936,7 +3102,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -2944,7 +3110,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -2952,22 +3118,22 @@
         <v>471</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C7" s="6" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C8" s="6" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -2975,27 +3141,27 @@
         <v>475</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="C10" s="6" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C12" s="6" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C13" s="6" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -3003,7 +3169,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -3011,7 +3177,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -3019,7 +3185,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -3027,7 +3193,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -3035,7 +3201,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -3043,7 +3209,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -3051,7 +3217,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -3059,197 +3225,200 @@
         <v>489</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B23" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>492</v>
-      </c>
       <c r="C23" s="6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="3" t="s">
+        <v>491</v>
+      </c>
       <c r="C25" s="6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C26" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B27" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B28" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B27" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B37" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B38" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B37" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C37" s="6" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C39" s="6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B40" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B41" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B38" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B40" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B41" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C42" s="6" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -3261,16 +3430,16 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9AFAB1-D13F-453B-A764-71BC4DD03FA9}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3296,57 +3465,57 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>468</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -3354,220 +3523,225 @@
         <v>116</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C15" s="6" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C20" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B21" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="B23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B25" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C26" s="6" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B27" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C25" s="6" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C28" s="6" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>7</v>
+        <v>549</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B32" s="3" t="s">
+        <v>282</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="6" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B35" s="3" t="s">
-        <v>116</v>
-      </c>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C35" s="6" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
       <c r="C37" s="6" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="6" t="s">
-        <v>553</v>
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C38" s="6" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C40" s="6" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -3579,16 +3753,16 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930164D6-DE97-4948-9170-1B29F324C0A0}">
-  <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3614,41 +3788,41 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>463</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C5" s="6" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -3656,336 +3830,347 @@
         <v>426</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C8" s="6" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C10" s="6" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C11" s="6" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>463</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C21" s="6" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>282</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B27" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="3" t="s">
-        <v>12</v>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>564</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B40" s="8" t="s">
+        <v>561</v>
+      </c>
       <c r="C40" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C42" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C43" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C44" s="6" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C45" s="6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C42" s="6" t="s">
+    <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C43" s="6" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C44" s="6" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="6" t="s">
+    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="6" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C51" s="6" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="6" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="2" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="C50" s="6" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>604</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -3998,15 +4183,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{307336A0-8DF1-492D-89DC-9934A1DE74C4}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4032,137 +4217,137 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>94</v>
       </c>
@@ -4170,72 +4355,419 @@
         <v>635</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C21" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C22" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C23" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C24" s="6" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C25" s="6" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C21" s="6" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C22" s="6" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C23" s="6" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
-      <c r="C24" s="6" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C25" s="6" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C27" s="6" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C29" s="6" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C30" s="6" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C32" s="6" t="s">
-        <v>623</v>
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37DFEF17-DF38-4A82-AA2F-3CCBF4CC5EB7}">
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="C2" s="6" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="C8" s="6" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="C9" s="6" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="C10" s="6" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="C11" s="6" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="C13" s="6" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="C14" s="6" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
+      <c r="C15" s="6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C18" s="6" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C23" s="6" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C25" s="6" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C26" s="6" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C27" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C28" s="6" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C30" s="6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C31" s="6" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C32" s="6" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C35" s="6" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C37" s="6" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C39" s="6" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C40" s="6" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C41" s="7" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C42" s="6" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C44" s="6" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C45" s="6" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C46" s="6" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C47" s="6" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C48" s="6" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B49" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B50" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C51" s="6" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C52" s="6" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -4248,15 +4780,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7115359D-7475-477E-8932-F919DE4EA60B}">
   <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4282,12 +4814,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
@@ -4295,7 +4827,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -4303,7 +4835,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -4311,7 +4843,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -4322,7 +4854,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4330,7 +4862,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -4341,12 +4873,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C9" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
@@ -4354,7 +4886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
@@ -4362,12 +4894,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C12" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
@@ -4375,7 +4907,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
@@ -4383,12 +4915,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C15" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -4396,7 +4928,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
@@ -4404,7 +4936,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
@@ -4412,7 +4944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -4420,7 +4952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -4428,17 +4960,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C21" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C22" s="7" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
@@ -4446,7 +4978,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
@@ -4454,12 +4986,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C25" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
@@ -4467,7 +4999,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
@@ -4475,27 +5007,27 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C28" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C29" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
@@ -4503,7 +5035,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -4511,7 +5043,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
@@ -4519,7 +5051,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
@@ -4527,17 +5059,17 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -4545,17 +5077,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C40" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>10</v>
       </c>
@@ -4563,7 +5095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>10</v>
       </c>
@@ -4571,7 +5103,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
@@ -4579,17 +5111,17 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C44" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C45" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
         <v>86</v>
       </c>
@@ -4597,12 +5129,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C47" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
         <v>91</v>
       </c>
@@ -4610,12 +5142,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C49" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>7</v>
       </c>
@@ -4623,7 +5155,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
         <v>94</v>
       </c>
@@ -4631,12 +5163,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>96</v>
       </c>
@@ -4644,22 +5176,22 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C55" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C56" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
         <v>96</v>
       </c>
@@ -4667,7 +5199,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
         <v>96</v>
       </c>
@@ -4675,7 +5207,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
         <v>96</v>
       </c>
@@ -4683,7 +5215,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>96</v>
       </c>
@@ -4691,12 +5223,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C61" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4704,12 +5236,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C63" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B64" s="3" t="s">
         <v>96</v>
       </c>
@@ -4717,7 +5249,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>7</v>
       </c>
@@ -4725,7 +5257,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>7</v>
       </c>
@@ -4733,7 +5265,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
         <v>96</v>
       </c>
@@ -4741,7 +5273,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B68" s="3" t="s">
         <v>96</v>
       </c>
@@ -4749,7 +5281,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
@@ -4757,7 +5289,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
         <v>116</v>
       </c>
@@ -4765,7 +5297,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B71" s="3" t="s">
         <v>116</v>
       </c>
@@ -4773,12 +5305,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C72" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B73" s="3" t="s">
         <v>455</v>
       </c>
@@ -4786,7 +5318,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
@@ -4794,7 +5326,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B75" s="3" t="s">
         <v>116</v>
       </c>
@@ -4802,7 +5334,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
         <v>116</v>
       </c>
@@ -4820,15 +5352,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EB44A9-9BB2-4DDC-B33A-B25D27D1D6DE}">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -4854,17 +5386,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -4872,7 +5404,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -4880,7 +5412,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -4888,7 +5420,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>455</v>
       </c>
@@ -4896,7 +5428,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>455</v>
       </c>
@@ -4904,7 +5436,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -4912,7 +5444,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>455</v>
       </c>
@@ -4920,7 +5452,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -4928,7 +5460,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>53</v>
       </c>
@@ -4936,7 +5468,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>116</v>
       </c>
@@ -4944,7 +5476,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
@@ -4952,17 +5484,17 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C15" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>94</v>
       </c>
@@ -4970,7 +5502,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>455</v>
       </c>
@@ -4978,7 +5510,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -4986,7 +5518,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>455</v>
       </c>
@@ -4994,7 +5526,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>142</v>
       </c>
@@ -5002,12 +5534,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
@@ -5015,7 +5547,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>455</v>
       </c>
@@ -5023,7 +5555,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>455</v>
       </c>
@@ -5031,7 +5563,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>7</v>
       </c>
@@ -5039,7 +5571,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>455</v>
       </c>
@@ -5047,7 +5579,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>455</v>
       </c>
@@ -5055,7 +5587,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>455</v>
       </c>
@@ -5073,15 +5605,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB64E87-5691-4BF1-B88C-0D9BCA723708}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -5107,17 +5639,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>456</v>
       </c>
@@ -5125,7 +5657,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>116</v>
       </c>
@@ -5133,7 +5665,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
@@ -5141,7 +5673,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
@@ -5149,12 +5681,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C8" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>116</v>
       </c>
@@ -5162,7 +5694,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -5170,7 +5702,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>116</v>
       </c>
@@ -5178,7 +5710,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>116</v>
       </c>
@@ -5186,7 +5718,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>116</v>
       </c>
@@ -5194,7 +5726,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>116</v>
       </c>
@@ -5202,7 +5734,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>116</v>
       </c>
@@ -5210,7 +5742,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -5218,12 +5750,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C17" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
@@ -5231,32 +5763,32 @@
         <v>159</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C19" s="6" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C22" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C23" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
@@ -5264,12 +5796,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C25" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
@@ -5277,7 +5809,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>116</v>
       </c>
@@ -5285,7 +5817,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>116</v>
       </c>
@@ -5293,17 +5825,17 @@
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C30" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
@@ -5311,7 +5843,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
@@ -5319,7 +5851,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>116</v>
       </c>
@@ -5327,7 +5859,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>116</v>
       </c>
@@ -5335,12 +5867,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C35" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>116</v>
       </c>
@@ -5351,7 +5883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>116</v>
       </c>
@@ -5362,7 +5894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>116</v>
       </c>
@@ -5373,7 +5905,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>116</v>
       </c>
@@ -5381,7 +5913,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>116</v>
       </c>
@@ -5389,7 +5921,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
@@ -5397,7 +5929,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
@@ -5405,7 +5937,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>116</v>
       </c>
@@ -5413,7 +5945,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
         <v>12</v>
       </c>
@@ -5421,7 +5953,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
         <v>12</v>
       </c>
@@ -5429,22 +5961,22 @@
         <v>207</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C46" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C47" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B49" s="3" t="s">
         <v>94</v>
       </c>
@@ -5452,7 +5984,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
         <v>94</v>
       </c>
@@ -5460,12 +5992,12 @@
         <v>172</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B52" s="3" t="s">
         <v>12</v>
       </c>
@@ -5473,7 +6005,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>7</v>
       </c>
@@ -5481,7 +6013,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B54" s="3" t="s">
         <v>12</v>
       </c>
@@ -5489,17 +6021,17 @@
         <v>208</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C55" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C56" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
@@ -5507,7 +6039,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
         <v>116</v>
       </c>
@@ -5515,12 +6047,12 @@
         <v>202</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C59" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -5528,7 +6060,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B61" s="3" t="s">
         <v>10</v>
       </c>
@@ -5536,7 +6068,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C62" s="6" t="s">
         <v>179</v>
       </c>
@@ -5551,15 +6083,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85819A9-A6A1-4AA6-96F8-1AFF8AF47654}">
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -5585,12 +6117,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>116</v>
       </c>
@@ -5598,7 +6130,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>116</v>
       </c>
@@ -5606,7 +6138,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
@@ -5614,17 +6146,17 @@
         <v>254</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C7" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
@@ -5632,7 +6164,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -5640,7 +6172,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -5648,7 +6180,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
@@ -5656,12 +6188,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>215</v>
       </c>
@@ -5669,12 +6201,12 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C14" s="6" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
@@ -5682,7 +6214,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>215</v>
       </c>
@@ -5690,7 +6222,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>215</v>
       </c>
@@ -5698,7 +6230,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>215</v>
       </c>
@@ -5706,7 +6238,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>10</v>
       </c>
@@ -5714,7 +6246,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -5722,7 +6254,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>10</v>
       </c>
@@ -5730,7 +6262,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>215</v>
       </c>
@@ -5738,7 +6270,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>215</v>
       </c>
@@ -5746,7 +6278,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -5754,12 +6286,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C25" s="6" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>215</v>
       </c>
@@ -5767,12 +6299,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C27" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
@@ -5780,7 +6312,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>215</v>
       </c>
@@ -5788,7 +6320,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
@@ -5796,12 +6328,12 @@
         <v>242</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>215</v>
       </c>
@@ -5809,7 +6341,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>12</v>
       </c>
@@ -5817,7 +6349,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>215</v>
       </c>
@@ -5825,12 +6357,12 @@
         <v>231</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C35" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>215</v>
       </c>
@@ -5838,7 +6370,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
@@ -5846,7 +6378,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>215</v>
       </c>
@@ -5854,7 +6386,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>215</v>
       </c>
@@ -5862,7 +6394,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>10</v>
       </c>
@@ -5870,7 +6402,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>215</v>
       </c>
@@ -5878,7 +6410,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>10</v>
       </c>
@@ -5886,7 +6418,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>215</v>
       </c>
@@ -5894,7 +6426,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -5902,7 +6434,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>7</v>
       </c>
@@ -5910,7 +6442,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
         <v>215</v>
       </c>
@@ -5918,7 +6450,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
         <v>215</v>
       </c>
@@ -5936,15 +6468,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967F6D5D-D295-422A-9553-A28D16FBCF3E}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -5970,7 +6502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>116</v>
       </c>
@@ -5978,22 +6510,22 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C4" s="6" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C5" s="6" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>116</v>
       </c>
@@ -6001,7 +6533,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -6009,7 +6541,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
@@ -6017,7 +6549,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>116</v>
       </c>
@@ -6025,7 +6557,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -6033,22 +6565,22 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C11" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C12" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>116</v>
       </c>
@@ -6056,12 +6588,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="C15" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
@@ -6069,12 +6601,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C17" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
@@ -6082,7 +6614,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>116</v>
       </c>
@@ -6090,12 +6622,12 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>116</v>
       </c>
@@ -6103,7 +6635,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>12</v>
       </c>
@@ -6111,7 +6643,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
@@ -6119,7 +6651,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
@@ -6137,15 +6669,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A7FE47-AF86-403F-8DF9-F647B1E34428}">
   <dimension ref="A1:H82"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -6171,7 +6703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
@@ -6179,7 +6711,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>116</v>
       </c>
@@ -6187,7 +6719,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>116</v>
       </c>
@@ -6195,12 +6727,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="C5" s="6" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>282</v>
       </c>
@@ -6208,7 +6740,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>116</v>
       </c>
@@ -6216,7 +6748,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>282</v>
       </c>
@@ -6224,22 +6756,22 @@
         <v>284</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C10" s="6" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C11" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>282</v>
       </c>
@@ -6247,7 +6779,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>116</v>
       </c>
@@ -6255,7 +6787,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>282</v>
       </c>
@@ -6263,7 +6795,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>116</v>
       </c>
@@ -6271,7 +6803,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>282</v>
       </c>
@@ -6279,7 +6811,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>116</v>
       </c>
@@ -6287,7 +6819,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>282</v>
       </c>
@@ -6295,7 +6827,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>282</v>
       </c>
@@ -6303,7 +6835,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
@@ -6311,7 +6843,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>116</v>
       </c>
@@ -6319,7 +6851,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>282</v>
       </c>
@@ -6327,7 +6859,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
@@ -6335,7 +6867,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
@@ -6343,7 +6875,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>282</v>
       </c>
@@ -6351,12 +6883,12 @@
         <v>355</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C26" s="6" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>116</v>
       </c>
@@ -6364,7 +6896,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>282</v>
       </c>
@@ -6372,17 +6904,17 @@
         <v>356</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C29" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C30" s="6" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
@@ -6390,7 +6922,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -6401,7 +6933,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>7</v>
       </c>
@@ -6409,7 +6941,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
@@ -6420,7 +6952,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>116</v>
       </c>
@@ -6428,7 +6960,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>116</v>
       </c>
@@ -6436,22 +6968,22 @@
         <v>336</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C38" s="6" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>293</v>
       </c>
@@ -6459,7 +6991,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
@@ -6467,7 +6999,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>116</v>
       </c>
@@ -6475,7 +7007,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>116</v>
       </c>
@@ -6483,12 +7015,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
         <v>116</v>
       </c>
@@ -6496,7 +7028,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
         <v>116</v>
       </c>
@@ -6504,7 +7036,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
         <v>116</v>
       </c>
@@ -6512,7 +7044,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
         <v>116</v>
       </c>
@@ -6520,7 +7052,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B49" s="3" t="s">
         <v>10</v>
       </c>
@@ -6528,7 +7060,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
         <v>10</v>
       </c>
@@ -6536,7 +7068,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
         <v>116</v>
       </c>
@@ -6544,7 +7076,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B52" s="3" t="s">
         <v>116</v>
       </c>
@@ -6552,7 +7084,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>10</v>
       </c>
@@ -6560,22 +7092,22 @@
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C54" s="6" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C55" s="6" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C56" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
         <v>12</v>
       </c>
@@ -6583,7 +7115,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>7</v>
       </c>
@@ -6591,12 +7123,12 @@
         <v>305</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>10</v>
       </c>
@@ -6604,17 +7136,17 @@
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C61" s="6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C62" s="6" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B63" s="3" t="s">
         <v>116</v>
       </c>
@@ -6622,7 +7154,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B64" s="3" t="s">
         <v>10</v>
       </c>
@@ -6630,7 +7162,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B65" s="3" t="s">
         <v>12</v>
       </c>
@@ -6638,7 +7170,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B66" s="3" t="s">
         <v>12</v>
       </c>
@@ -6646,7 +7178,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
         <v>116</v>
       </c>
@@ -6654,7 +7186,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B68" s="3" t="s">
         <v>116</v>
       </c>
@@ -6662,12 +7194,12 @@
         <v>344</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C69" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>7</v>
       </c>
@@ -6675,7 +7207,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>7</v>
       </c>
@@ -6683,7 +7215,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
@@ -6691,12 +7223,12 @@
         <v>314</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C73" s="6" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
@@ -6704,7 +7236,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B75" s="3" t="s">
         <v>10</v>
       </c>
@@ -6712,12 +7244,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C76" s="6" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B77" s="3" t="s">
         <v>116</v>
       </c>
@@ -6725,7 +7257,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B78" s="3" t="s">
         <v>12</v>
       </c>
@@ -6733,7 +7265,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B79" s="3" t="s">
         <v>116</v>
       </c>
@@ -6741,7 +7273,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B80" s="3" t="s">
         <v>116</v>
       </c>
@@ -6749,12 +7281,12 @@
         <v>346</v>
       </c>
     </row>
-    <row r="81" spans="3:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C81" s="6" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="82" spans="3:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C82" s="6" t="s">
         <v>304</v>
       </c>
@@ -6769,15 +7301,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A100192-05EB-4836-9F6B-C6DB0E932DAB}">
   <dimension ref="A1:H94"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
-    <col min="4" max="8" width="8.625" style="2"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
+    <col min="4" max="8" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -6803,12 +7335,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>366</v>
       </c>
@@ -6816,7 +7348,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>116</v>
       </c>
@@ -6824,7 +7356,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>366</v>
       </c>
@@ -6832,7 +7364,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>116</v>
       </c>
@@ -6840,12 +7372,12 @@
         <v>436</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C7" s="6" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>116</v>
       </c>
@@ -6853,7 +7385,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>366</v>
       </c>
@@ -6861,22 +7393,22 @@
         <v>368</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C10" s="6" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C11" s="6" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>116</v>
       </c>
@@ -6884,12 +7416,12 @@
         <v>438</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C14" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -6897,7 +7429,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -6905,12 +7437,12 @@
         <v>373</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C17" s="6" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
@@ -6918,7 +7450,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -6926,7 +7458,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
@@ -6934,7 +7466,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>116</v>
       </c>
@@ -6942,7 +7474,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>116</v>
       </c>
@@ -6950,22 +7482,22 @@
         <v>442</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C23" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C24" s="6" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>366</v>
       </c>
@@ -6973,17 +7505,17 @@
         <v>414</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C27" s="6" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C28" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
@@ -6991,7 +7523,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
@@ -6999,12 +7531,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>366</v>
       </c>
@@ -7012,12 +7544,12 @@
         <v>453</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C33" s="6" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>7</v>
       </c>
@@ -7025,7 +7557,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>12</v>
       </c>
@@ -7033,12 +7565,12 @@
         <v>434</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C36" s="6" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>7</v>
       </c>
@@ -7046,7 +7578,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>116</v>
       </c>
@@ -7054,7 +7586,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>10</v>
       </c>
@@ -7062,7 +7594,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>366</v>
       </c>
@@ -7070,12 +7602,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C41" s="6" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
@@ -7083,7 +7615,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>10</v>
       </c>
@@ -7091,7 +7623,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
@@ -7099,7 +7631,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
         <v>10</v>
       </c>
@@ -7107,17 +7639,17 @@
         <v>420</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C46" s="6" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
         <v>366</v>
       </c>
@@ -7125,12 +7657,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C49" s="6" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
         <v>116</v>
       </c>
@@ -7138,12 +7670,12 @@
         <v>444</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C51" s="6" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>7</v>
       </c>
@@ -7151,12 +7683,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C53" s="6" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -7164,7 +7696,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
@@ -7175,7 +7707,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -7186,7 +7718,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>7</v>
       </c>
@@ -7194,7 +7726,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
@@ -7205,7 +7737,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -7216,7 +7748,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>116</v>
       </c>
@@ -7224,7 +7756,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B61" s="3" t="s">
         <v>116</v>
       </c>
@@ -7232,7 +7764,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>7</v>
       </c>
@@ -7240,27 +7772,27 @@
         <v>399</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C63" s="6" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C64" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C65" s="6" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
         <v>10</v>
       </c>
@@ -7268,7 +7800,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -7276,7 +7808,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>7</v>
       </c>
@@ -7284,7 +7816,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
         <v>10</v>
       </c>
@@ -7292,12 +7824,12 @@
         <v>422</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
@@ -7305,12 +7837,12 @@
         <v>423</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C73" s="6" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
         <v>10</v>
       </c>
@@ -7318,12 +7850,12 @@
         <v>424</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C75" s="6" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
         <v>10</v>
       </c>
@@ -7331,12 +7863,12 @@
         <v>425</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C77" s="6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>7</v>
       </c>
@@ -7344,7 +7876,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>11</v>
       </c>
@@ -7355,7 +7887,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -7366,7 +7898,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -7377,7 +7909,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -7388,7 +7920,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -7399,7 +7931,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>7</v>
       </c>
@@ -7407,7 +7939,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>11</v>
       </c>
@@ -7418,7 +7950,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
@@ -7429,7 +7961,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -7440,7 +7972,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -7451,7 +7983,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
@@ -7462,12 +7994,12 @@
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C90" s="6" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="B91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7475,7 +8007,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B92" s="3" t="s">
         <v>10</v>
       </c>
@@ -7483,7 +8015,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B93" s="3" t="s">
         <v>10</v>
       </c>
@@ -7491,7 +8023,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C94" s="6" t="s">
         <v>412</v>
       </c>
@@ -7506,15 +8038,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA34A18B-B515-443B-8160-8DC81D3CB263}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" style="6" customWidth="1"/>
     <col min="4" max="8" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -7540,22 +8072,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="48" x14ac:dyDescent="0.45">
       <c r="C3" s="6" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="C4" s="6" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>461</v>
       </c>
@@ -7563,7 +8095,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>116</v>
       </c>
@@ -7571,7 +8103,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>116</v>
       </c>
@@ -7579,7 +8111,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>86</v>
       </c>
@@ -7587,7 +8119,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>116</v>
       </c>
@@ -7595,7 +8127,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>468</v>
       </c>
@@ -7603,7 +8135,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>468</v>
       </c>
@@ -7611,7 +8143,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>461</v>
       </c>
@@ -7619,7 +8151,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>461</v>
       </c>
